--- a/datos puntaje.xlsx
+++ b/datos puntaje.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianamazuera/Desktop/USI/TESIS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianamazuera/Desktop/OTRO/USI/PhD/ROUND 5/DATOS USI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B484FE-268E-394A-9971-3A69DB8DCE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B2C747-6520-5447-AA79-0184A8C014B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="28800" windowHeight="17520" activeTab="9" xr2:uid="{31929B93-7941-9444-8B39-C13845CB9202}"/>
+    <workbookView xWindow="4320" yWindow="620" windowWidth="24480" windowHeight="15880" activeTab="10" xr2:uid="{31929B93-7941-9444-8B39-C13845CB9202}"/>
   </bookViews>
   <sheets>
     <sheet name="FUENTES" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1338,10 +1338,10 @@
     <t>k</t>
   </si>
   <si>
-    <t>indice de percepcion de corrupcion de 2002-2022</t>
+    <t>indice de buena gobernazan - control de corrupcion. Banco mundial 2002-2022</t>
   </si>
   <si>
-    <t>indice de buena gobernazan - control de corrupcion. Banco mundial 2002-2022</t>
+    <t>indice de percepcion de corrupcion de 2002-2022 - Transparencia Internacional</t>
   </si>
 </sst>
 </file>
@@ -21836,7 +21836,7 @@
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="56"/>
       <c r="B1" s="70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
@@ -22474,7 +22474,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B1" s="70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="70"/>
